--- a/DRIVE/3. Operações/3.1 Projetos/26002 - SS AEISEP (Porto)/Peças escritas/ORÇAMENTO V1 POR-2026-0002-SSYS.xlsx
+++ b/DRIVE/3. Operações/3.1 Projetos/26002 - SS AEISEP (Porto)/Peças escritas/ORÇAMENTO V1 POR-2026-0002-SSYS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\MINDSET\DRIVE\3. Operações\3.1 Projetos\26002 - SS AEISEP (Porto)\Peças escritas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C888C97-02F6-4182-98EE-BAD52A845119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905CE3EB-83D6-4EF2-AB46-BC2ACAE491DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Proposta!$A$1:$G$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Proposta!$A$1:$G$62</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>PROPOSTA DE FORNECIMENTO</t>
   </si>
@@ -45,9 +47,6 @@
     <t>[NIF do cliente]</t>
   </si>
   <si>
-    <t>A confirmar</t>
-  </si>
-  <si>
     <t>DESIGNAÇÃO / DESCRIÇÃO</t>
   </si>
   <si>
@@ -63,9 +62,6 @@
     <t>AE ISEP</t>
   </si>
   <si>
-    <t>Pago na encomenda</t>
-  </si>
-  <si>
     <t>MINDSET soundsystem</t>
   </si>
   <si>
@@ -78,9 +74,6 @@
     <t>CONDIÇÕES PAGAMENTO:</t>
   </si>
   <si>
-    <t>Até aprovação do cliente</t>
-  </si>
-  <si>
     <t>mind7sound@outllook.com</t>
   </si>
   <si>
@@ -132,19 +125,22 @@
     <t>3-Pin XLR c/ fichas Amphenol</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>TOTAL S/ IVA</t>
   </si>
   <si>
     <t>NOTAS: Portes de envio a decidir. Preços por unidade apresentados não incluem IVA.Orçamento sujeito a revisões.</t>
   </si>
   <si>
-    <t>Mão de obra especializada</t>
-  </si>
-  <si>
-    <t>Mão de obra</t>
+    <t>Pré-pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acessórios e Utilitários </t>
+  </si>
+  <si>
+    <t>Conectores, junções, etc</t>
+  </si>
+  <si>
+    <t>30 dias</t>
   </si>
 </sst>
 </file>
@@ -154,7 +150,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,13 +256,6 @@
     <font>
       <b/>
       <sz val="8"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color rgb="FF1A1A1A"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -492,7 +481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -516,9 +505,6 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -557,11 +543,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -570,13 +555,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -621,6 +606,7 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -937,7 +923,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -951,15 +937,15 @@
   <sheetData>
     <row r="1" spans="1:7" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="57" t="s">
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="57"/>
-      <c r="G2" s="40"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="38"/>
     </row>
     <row r="3" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -967,71 +953,71 @@
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
-      <c r="B4" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>7</v>
+      <c r="B4" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>6</v>
       </c>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="20">
+      <c r="B5" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="19">
         <v>46137</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="23" t="s">
+      <c r="D5" s="20"/>
+      <c r="E5" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="22" t="s">
         <v>1</v>
       </c>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="20"/>
+      <c r="E6" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="25"/>
+      <c r="B7" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="19">
+        <v>46147</v>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
-      <c r="B7" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
@@ -1043,36 +1029,36 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="30"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="42" t="s">
+      <c r="B10" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="E10" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="F10" s="42" t="s">
         <v>5</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>6</v>
       </c>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="55">
+      <c r="B11" s="53">
         <v>1</v>
       </c>
       <c r="C11" s="9"/>
@@ -1083,37 +1069,38 @@
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="55"/>
+      <c r="B12" s="53"/>
       <c r="C12" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D12" s="7">
-        <v>102.5</v>
+        <f>102.5*1.13</f>
+        <v>115.82499999999999</v>
       </c>
       <c r="E12" s="8">
         <f>B11*D12</f>
-        <v>102.5</v>
-      </c>
-      <c r="F12" s="14">
+        <v>115.82499999999999</v>
+      </c>
+      <c r="F12" s="13">
         <f>E12</f>
-        <v>102.5</v>
+        <v>115.82499999999999</v>
       </c>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="56"/>
-      <c r="C13" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="54">
+      <c r="B14" s="52">
         <v>2</v>
       </c>
       <c r="C14" s="9"/>
@@ -1124,37 +1111,38 @@
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="55"/>
+      <c r="B15" s="53"/>
       <c r="C15" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D15" s="7">
-        <v>101</v>
+        <f>101*1.13</f>
+        <v>114.13</v>
       </c>
       <c r="E15" s="8">
-        <f>B14*D15</f>
-        <v>202</v>
-      </c>
-      <c r="F15" s="14">
+        <f>D15*B14</f>
+        <v>228.26</v>
+      </c>
+      <c r="F15" s="13">
         <f>E15</f>
-        <v>202</v>
+        <v>228.26</v>
       </c>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="54">
+      <c r="B17" s="52">
         <v>1</v>
       </c>
       <c r="C17" s="9"/>
@@ -1165,37 +1153,38 @@
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="55"/>
+      <c r="B18" s="53"/>
       <c r="C18" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D18" s="7">
-        <v>126</v>
+        <f>126*1.12</f>
+        <v>141.12</v>
       </c>
       <c r="E18" s="8">
-        <f>B17*D18</f>
-        <v>126</v>
-      </c>
-      <c r="F18" s="14">
+        <f>D18*B17</f>
+        <v>141.12</v>
+      </c>
+      <c r="F18" s="13">
         <f>E18</f>
-        <v>126</v>
+        <v>141.12</v>
       </c>
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="30"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="30"/>
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="54">
+      <c r="B20" s="52">
         <v>4</v>
       </c>
       <c r="C20" s="9"/>
@@ -1206,37 +1195,38 @@
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="55"/>
+      <c r="B21" s="53"/>
       <c r="C21" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D21" s="7">
-        <v>48</v>
+        <f>48*1.12</f>
+        <v>53.760000000000005</v>
       </c>
       <c r="E21" s="8">
         <f>B20*D21</f>
-        <v>192</v>
-      </c>
-      <c r="F21" s="14">
+        <v>215.04000000000002</v>
+      </c>
+      <c r="F21" s="13">
         <f>E21</f>
-        <v>192</v>
+        <v>215.04000000000002</v>
       </c>
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="54">
+      <c r="B23" s="52">
         <v>1</v>
       </c>
       <c r="C23" s="9"/>
@@ -1247,174 +1237,113 @@
     </row>
     <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="55"/>
+      <c r="B24" s="53"/>
       <c r="C24" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D24" s="7">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="E24" s="8">
-        <v>150</v>
-      </c>
-      <c r="F24" s="14">
+        <f>D24*B23</f>
+        <v>50</v>
+      </c>
+      <c r="F24" s="13">
         <f>E24</f>
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="10"/>
-    </row>
-    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="11"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
-      <c r="B27" s="55"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="14"/>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
       <c r="G28" s="2"/>
     </row>
-    <row r="29" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="10"/>
+      <c r="G29" s="2"/>
     </row>
     <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="B30" s="55"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="14"/>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="10"/>
-    </row>
-    <row r="32" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="B32" s="54"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="10"/>
-    </row>
-    <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
-      <c r="B33" s="55"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="10"/>
+      <c r="G33" s="2"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="10"/>
-    </row>
-    <row r="35" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="54"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="10"/>
-    </row>
-    <row r="36" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="55"/>
-      <c r="C36" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="14"/>
       <c r="G36" s="2"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="26"/>
-      <c r="B37" s="56"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="32"/>
-    </row>
-    <row r="38" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="D38" s="11"/>
-      <c r="F38" s="12"/>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="1:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="G45" s="2"/>
     </row>
@@ -1466,79 +1395,67 @@
       <c r="A57" s="1"/>
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="1"/>
-      <c r="G58" s="2"/>
+    <row r="58" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="43"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" s="45"/>
+      <c r="F58" s="46">
+        <f>SUM(F12,F15,F18,F24,F21)</f>
+        <v>750.24499999999989</v>
+      </c>
+      <c r="G58" s="47"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="G59" s="2"/>
     </row>
-    <row r="60" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="45"/>
-      <c r="B60" s="46"/>
-      <c r="C60" s="46"/>
-      <c r="D60" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="E60" s="47"/>
-      <c r="F60" s="48">
-        <f>F12+F15+F18+F21+F24+F27+F30+F33+F36</f>
-        <v>772.5</v>
-      </c>
-      <c r="G60" s="49"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="1"/>
-      <c r="G61" s="2"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="58" t="s">
-        <v>33</v>
-      </c>
-      <c r="B62" s="59"/>
-      <c r="C62" s="59"/>
-      <c r="D62" s="59"/>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="58"/>
+    </row>
+    <row r="61" spans="1:7" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="31"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="33"/>
+    </row>
+    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="48"/>
+      <c r="B62" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="50"/>
+      <c r="D62" s="59" t="s">
+        <v>11</v>
+      </c>
       <c r="E62" s="59"/>
       <c r="F62" s="59"/>
-      <c r="G62" s="60"/>
-    </row>
-    <row r="63" spans="1:7" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="33"/>
-      <c r="B63" s="34"/>
-      <c r="C63" s="34"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="34"/>
-      <c r="F63" s="34"/>
-      <c r="G63" s="35"/>
-    </row>
-    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="50"/>
-      <c r="B64" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" s="52"/>
-      <c r="D64" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="61"/>
-      <c r="F64" s="61"/>
-      <c r="G64" s="53"/>
+      <c r="G62" s="51"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="B35:B37"/>
+  <mergeCells count="8">
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="D62:F62"/>
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="B29:B31"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="87" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
